--- a/reports/tracker.xlsx
+++ b/reports/tracker.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Founder Targets" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Job Listings'!$A$1:$N$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Job Listings'!$A$1:$P$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -40,9 +40,21 @@
     </font>
     <font>
       <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00146B5F"/>
+      <sz val="10"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <color rgb="001F3A5F"/>
       <sz val="10"/>
       <u val="single"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <color rgb="003D454E"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -81,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -93,9 +105,15 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -461,23 +479,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="58" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="42" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="52" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="40" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -538,15 +558,25 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Link</t>
+          <t>Apply</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>JD Link</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Tailor Command</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>Applied?</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -596,11 +626,21 @@
       </c>
       <c r="L2" s="4" t="inlineStr">
         <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
           <t>https://apply.workable.com/j/E7CD7FB957</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="3" t="inlineStr">
+      <c r="N2" s="6" t="inlineStr">
+        <is>
+          <t>node scripts/tailor.mjs --url "https://apply.workable.com/j/E7CD7FB957" --company "Innovaccer" --title "4403 - Software Development Engineer-II (Finance - AI Engineering)"</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr"/>
+      <c r="P2" s="3" t="inlineStr">
         <is>
           <t>On-site or hybrid at a named Indian location.</t>
         </is>
@@ -654,11 +694,21 @@
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
           <t>https://jobs.ashbyhq.com/supabase/06752423-eebb-472c-95b5-c7ff2559fd60</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr"/>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="N3" s="6" t="inlineStr">
+        <is>
+          <t>node scripts/tailor.mjs --url "https://jobs.ashbyhq.com/supabase/06752423-eebb-472c-95b5-c7ff2559fd60" --company "Supabase" --title "Software Engineer - Branching"</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr"/>
+      <c r="P3" s="3" t="inlineStr">
         <is>
           <t>Worldwide or "anywhere" with no country lock stated.</t>
         </is>
@@ -708,11 +758,21 @@
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
           <t>https://job-boards.greenhouse.io/gitlab/jobs/8556658002</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="3" t="inlineStr">
+      <c r="N4" s="6" t="inlineStr">
+        <is>
+          <t>node scripts/tailor.mjs --url "https://job-boards.greenhouse.io/gitlab/jobs/8556658002" --company "GitLab" --title "AI Engineer"</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr"/>
+      <c r="P4" s="3" t="inlineStr">
         <is>
           <t>Remote and India is named explicitly. | Negative keywords: salesforce</t>
         </is>
@@ -766,11 +826,21 @@
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
           <t>https://jobs.ashbyhq.com/aiprise/02112df8-70fa-4133-a860-151b5f585ed9</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr"/>
-      <c r="N5" s="3" t="inlineStr">
+      <c r="N5" s="6" t="inlineStr">
+        <is>
+          <t>node scripts/tailor.mjs --url "https://jobs.ashbyhq.com/aiprise/02112df8-70fa-4133-a860-151b5f585ed9" --company "AiPrise" --title "Software Engineer II (Bangalore, India)"</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr"/>
+      <c r="P5" s="3" t="inlineStr">
         <is>
           <t>On-site or hybrid at a named Indian location.</t>
         </is>
@@ -784,7 +854,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Software Engineer III (Bangalore, India)</t>
+          <t>Software Engineer I (Bangalore, India)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -809,11 +879,7 @@
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>4+ yrs</t>
-        </is>
-      </c>
+      <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
           <t>2026-08-24</t>
@@ -824,11 +890,21 @@
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/aiprise/e7890d9f-8e1f-48a0-92be-071a282e7fe8</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
-      <c r="N6" s="3" t="inlineStr">
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="M6" s="5" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/aiprise/3763c791-a387-4078-9ca4-00cbfbf9b1a6</t>
+        </is>
+      </c>
+      <c r="N6" s="6" t="inlineStr">
+        <is>
+          <t>node scripts/tailor.mjs --url "https://jobs.ashbyhq.com/aiprise/3763c791-a387-4078-9ca4-00cbfbf9b1a6" --company "AiPrise" --title "Software Engineer I (Bangalore, India)"</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr"/>
+      <c r="P6" s="3" t="inlineStr">
         <is>
           <t>On-site or hybrid at a named Indian location.</t>
         </is>
@@ -842,7 +918,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Software Engineer I (Bangalore, India)</t>
+          <t>Software Engineer III (Bangalore, India)</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -867,22 +943,36 @@
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr"/>
-      <c r="I7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4+ yrs</t>
+        </is>
+      </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
       <c r="K7" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/aiprise/3763c791-a387-4078-9ca4-00cbfbf9b1a6</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
-      <c r="N7" s="3" t="inlineStr">
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="M7" s="5" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/aiprise/e7890d9f-8e1f-48a0-92be-071a282e7fe8</t>
+        </is>
+      </c>
+      <c r="N7" s="6" t="inlineStr">
+        <is>
+          <t>node scripts/tailor.mjs --url "https://jobs.ashbyhq.com/aiprise/e7890d9f-8e1f-48a0-92be-071a282e7fe8" --company "AiPrise" --title "Software Engineer III (Bangalore, India)"</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr"/>
+      <c r="P7" s="3" t="inlineStr">
         <is>
           <t>On-site or hybrid at a named Indian location.</t>
         </is>
@@ -932,11 +1022,21 @@
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="M8" s="5" t="inlineStr">
+        <is>
           <t>https://jobs.lever.co/netomi/0e6b7355-330a-4d10-b8d5-c235bd555622</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr"/>
-      <c r="N8" s="3" t="inlineStr">
+      <c r="N8" s="6" t="inlineStr">
+        <is>
+          <t>node scripts/tailor.mjs --url "https://jobs.lever.co/netomi/0e6b7355-330a-4d10-b8d5-c235bd555622" --company "Netomi" --title "Agentic Engineer Level II/III"</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr"/>
+      <c r="P8" s="3" t="inlineStr">
         <is>
           <t>Remote and India is named explicitly.</t>
         </is>
@@ -990,11 +1090,21 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="M9" s="5" t="inlineStr">
+        <is>
           <t>https://job-boards.greenhouse.io/dscout/jobs/4370258009</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr"/>
-      <c r="N9" s="3" t="inlineStr">
+      <c r="N9" s="6" t="inlineStr">
+        <is>
+          <t>node scripts/tailor.mjs --url "https://job-boards.greenhouse.io/dscout/jobs/4370258009" --company "Dscout" --title "Applied AI Engineer - India"</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr"/>
+      <c r="P9" s="3" t="inlineStr">
         <is>
           <t>Remote and India is named explicitly.</t>
         </is>
@@ -1048,11 +1158,21 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="M10" s="5" t="inlineStr">
+        <is>
           <t>https://job-boards.greenhouse.io/dscout/jobs/4370266009</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr"/>
-      <c r="N10" s="3" t="inlineStr">
+      <c r="N10" s="6" t="inlineStr">
+        <is>
+          <t>node scripts/tailor.mjs --url "https://job-boards.greenhouse.io/dscout/jobs/4370266009" --company "Dscout" --title "Software Engineer - India"</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr"/>
+      <c r="P10" s="3" t="inlineStr">
         <is>
           <t>Remote and India is named explicitly.</t>
         </is>
@@ -1102,11 +1222,21 @@
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="M11" s="5" t="inlineStr">
+        <is>
           <t>https://jobs.ashbyhq.com/sarvam/36f89b00-2010-4d23-aae3-17a2f53d9eaa</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr"/>
-      <c r="N11" s="3" t="inlineStr">
+      <c r="N11" s="6" t="inlineStr">
+        <is>
+          <t>node scripts/tailor.mjs --url "https://jobs.ashbyhq.com/sarvam/36f89b00-2010-4d23-aae3-17a2f53d9eaa" --company "Sarvam AI" --title "Agent Engineer"</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr"/>
+      <c r="P11" s="3" t="inlineStr">
         <is>
           <t>On-site or hybrid at a named Indian location.</t>
         </is>
@@ -1156,11 +1286,21 @@
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="M12" s="5" t="inlineStr">
+        <is>
           <t>https://job-boards.greenhouse.io/gleanwork/jobs/4722386005</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr"/>
-      <c r="N12" s="3" t="inlineStr">
+      <c r="N12" s="6" t="inlineStr">
+        <is>
+          <t>node scripts/tailor.mjs --url "https://job-boards.greenhouse.io/gleanwork/jobs/4722386005" --company "Glean" --title "Strategic Solutions Engineer, West"</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr"/>
+      <c r="P12" s="3" t="inlineStr">
         <is>
           <t>Plain "Remote" with no country lock stated. Verify India eligibility on the JD before applying. | Negative keywords: servicenow</t>
         </is>
@@ -1210,11 +1350,21 @@
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="M13" s="5" t="inlineStr">
+        <is>
           <t>https://job-boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4723067005</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr"/>
-      <c r="N13" s="3" t="inlineStr">
+      <c r="N13" s="6" t="inlineStr">
+        <is>
+          <t>node scripts/tailor.mjs --url "https://job-boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4723067005" --company "Razorpay" --title "Forward Deployed Engineer"</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr"/>
+      <c r="P13" s="3" t="inlineStr">
         <is>
           <t>On-site or hybrid at a named Indian location. | Negative keywords: salesforce</t>
         </is>
@@ -1264,11 +1414,21 @@
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="M14" s="5" t="inlineStr">
+        <is>
           <t>https://job-boards.greenhouse.io/automatticcareers/jobs/5862239</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr"/>
-      <c r="N14" s="3" t="inlineStr">
+      <c r="N14" s="6" t="inlineStr">
+        <is>
+          <t>node scripts/tailor.mjs --url "https://job-boards.greenhouse.io/automatticcareers/jobs/5862239" --company "Automattic" --title "Experienced Software Engineer"</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr"/>
+      <c r="P14" s="3" t="inlineStr">
         <is>
           <t>Plain "Remote" with no country lock stated. Verify India eligibility on the JD before applying. | Negative keywords: wordpress</t>
         </is>
@@ -1318,33 +1478,57 @@
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="M15" s="5" t="inlineStr">
+        <is>
           <t>https://job-boards.greenhouse.io/gleanwork/jobs/4712434005</t>
         </is>
       </c>
-      <c r="M15" s="2" t="inlineStr"/>
-      <c r="N15" s="3" t="inlineStr">
+      <c r="N15" s="6" t="inlineStr">
+        <is>
+          <t>node scripts/tailor.mjs --url "https://job-boards.greenhouse.io/gleanwork/jobs/4712434005" --company "Glean" --title "Software Engineer, Agents Governance"</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr"/>
+      <c r="P15" s="3" t="inlineStr">
         <is>
           <t>On-site or hybrid at a named Indian location. | Seniority: JD asks for 6+ years vs 2.7 — beyond the stretch band · Negative keywords: servicenow</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N15"/>
+  <autoFilter ref="A1:P15"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="rId28"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1356,24 +1540,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="50" customWidth="1" min="9" max="9"/>
-    <col width="44" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="34" customWidth="1" min="15" max="15"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="50" customWidth="1" min="10" max="10"/>
+    <col width="44" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="34" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -1389,72 +1574,77 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Careers Page</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Founder</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Domain</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Guessed Email</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Source/Round</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Email Draft</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>LinkedIn Draft</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Outreach Sent?</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Date Sent</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Follow-up Due</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Response?</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>VERIFY BEFORE SENDING — every Guessed Email is a first@domain guess, never a verified address; check it yourself (Hunter.io) first. Personalise every draft with one genuine observation about what they build. Nothing in this tab is ever sent automatically.</t>
         </is>
@@ -1462,7 +1652,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A2:O2"/>
+    <mergeCell ref="A2:P2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/tracker.xlsx
+++ b/reports/tracker.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Founder Targets" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Job Listings'!$A$1:$P$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Job Listings'!$A$1:$P$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P15"/>
+  <dimension ref="A1:P14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -585,23 +585,23 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>workable</t>
+          <t>lever</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>4403 - Software Development Engineer-II (Finance - AI Engineering)</t>
+          <t>Software Development Engineer II - Backend</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Innovaccer</t>
+          <t>HighLevel (GoHighLevel)</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr"/>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Noida, Uttar Pradesh, India</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -618,11 +618,11 @@
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="K2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2" s="4" t="inlineStr">
         <is>
@@ -631,12 +631,12 @@
       </c>
       <c r="M2" s="5" t="inlineStr">
         <is>
-          <t>https://apply.workable.com/j/E7CD7FB957</t>
+          <t>https://jobs.lever.co/gohighlevel/13c8402f-8cf0-4b09-b666-43e71b8b525e</t>
         </is>
       </c>
       <c r="N2" s="6" t="inlineStr">
         <is>
-          <t>node scripts/tailor.mjs --url "https://apply.workable.com/j/E7CD7FB957" --company "Innovaccer" --title "4403 - Software Development Engineer-II (Finance - AI Engineering)"</t>
+          <t>node scripts/tailor.mjs --url "https://jobs.lever.co/gohighlevel/13c8402f-8cf0-4b09-b666-43e71b8b525e" --company "HighLevel (GoHighLevel)" --title "Software Development Engineer II - Backend"</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr"/>
@@ -649,23 +649,23 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>ashby</t>
+          <t>lever</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Software Engineer - Branching</t>
+          <t>Software Development Engineer II - Frontend</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Supabase</t>
+          <t>HighLevel (GoHighLevel)</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr"/>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Remote, Global</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -675,22 +675,18 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>remote-global</t>
+          <t>india</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>3+ yrs</t>
-        </is>
-      </c>
+      <c r="I3" s="2" t="inlineStr"/>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="K3" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
@@ -699,41 +695,41 @@
       </c>
       <c r="M3" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/supabase/06752423-eebb-472c-95b5-c7ff2559fd60</t>
+          <t>https://jobs.lever.co/gohighlevel/b8dc97ec-a0b7-4195-9f3b-86440ff18f82</t>
         </is>
       </c>
       <c r="N3" s="6" t="inlineStr">
         <is>
-          <t>node scripts/tailor.mjs --url "https://jobs.ashbyhq.com/supabase/06752423-eebb-472c-95b5-c7ff2559fd60" --company "Supabase" --title "Software Engineer - Branching"</t>
+          <t>node scripts/tailor.mjs --url "https://jobs.lever.co/gohighlevel/b8dc97ec-a0b7-4195-9f3b-86440ff18f82" --company "HighLevel (GoHighLevel)" --title "Software Development Engineer II - Frontend"</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr"/>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>Worldwide or "anywhere" with no country lock stated.</t>
+          <t>On-site or hybrid at a named Indian location.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>workable</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>4403 - Software Development Engineer-II (Finance - AI Engineering)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>GitLab</t>
+          <t>Innovaccer</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Remote, Bangalore</t>
+          <t>Noida, Uttar Pradesh, India</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -743,18 +739,18 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>remote-global</t>
+          <t>india</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="K4" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
@@ -763,41 +759,41 @@
       </c>
       <c r="M4" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8556658002</t>
+          <t>https://apply.workable.com/j/E7CD7FB957</t>
         </is>
       </c>
       <c r="N4" s="6" t="inlineStr">
         <is>
-          <t>node scripts/tailor.mjs --url "https://job-boards.greenhouse.io/gitlab/jobs/8556658002" --company "GitLab" --title "AI Engineer"</t>
+          <t>node scripts/tailor.mjs --url "https://apply.workable.com/j/E7CD7FB957" --company "Innovaccer" --title "4403 - Software Development Engineer-II (Finance - AI Engineering)"</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr"/>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>Remote and India is named explicitly. | Negative keywords: salesforce</t>
+          <t>On-site or hybrid at a named Indian location. | Weak archetype match (best: sde-generalist @ 16)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>ashby</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Software Engineer II (Bangalore, India)</t>
+          <t>Intermediate Backend Engineer, India</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>AiPrise</t>
+          <t>GitLab</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr"/>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Bangalore, India</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -807,22 +803,18 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>india</t>
+          <t>remote-global</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>2+ yrs</t>
-        </is>
-      </c>
+      <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="K5" s="2" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
@@ -831,12 +823,12 @@
       </c>
       <c r="M5" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/aiprise/02112df8-70fa-4133-a860-151b5f585ed9</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8775507002</t>
         </is>
       </c>
       <c r="N5" s="6" t="inlineStr">
         <is>
-          <t>node scripts/tailor.mjs --url "https://jobs.ashbyhq.com/aiprise/02112df8-70fa-4133-a860-151b5f585ed9" --company "AiPrise" --title "Software Engineer II (Bangalore, India)"</t>
+          <t>node scripts/tailor.mjs --url "https://job-boards.greenhouse.io/gitlab/jobs/8775507002" --company "GitLab" --title "Intermediate Backend Engineer, India"</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr"/>
@@ -849,23 +841,23 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>ashby</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Software Engineer I (Bangalore, India)</t>
+          <t>Intermediate Backend Engineer</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>AiPrise</t>
+          <t>GitLab</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Bangalore, India</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -875,18 +867,18 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>india</t>
+          <t>remote-global</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="K6" s="2" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
@@ -895,12 +887,12 @@
       </c>
       <c r="M6" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/aiprise/3763c791-a387-4078-9ca4-00cbfbf9b1a6</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8736877002</t>
         </is>
       </c>
       <c r="N6" s="6" t="inlineStr">
         <is>
-          <t>node scripts/tailor.mjs --url "https://jobs.ashbyhq.com/aiprise/3763c791-a387-4078-9ca4-00cbfbf9b1a6" --company "AiPrise" --title "Software Engineer I (Bangalore, India)"</t>
+          <t>node scripts/tailor.mjs --url "https://job-boards.greenhouse.io/gitlab/jobs/8736877002" --company "GitLab" --title "Intermediate Backend Engineer"</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr"/>
@@ -918,18 +910,18 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Software Engineer III (Bangalore, India)</t>
+          <t>Software Engineer - Branching</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>AiPrise</t>
+          <t>Supabase</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr"/>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Remote, Global</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -939,22 +931,22 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>india</t>
+          <t>remote-global</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr"/>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4+ yrs</t>
+          <t>3+ yrs</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="K7" s="2" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
@@ -963,41 +955,41 @@
       </c>
       <c r="M7" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/aiprise/e7890d9f-8e1f-48a0-92be-071a282e7fe8</t>
+          <t>https://jobs.ashbyhq.com/supabase/06752423-eebb-472c-95b5-c7ff2559fd60</t>
         </is>
       </c>
       <c r="N7" s="6" t="inlineStr">
         <is>
-          <t>node scripts/tailor.mjs --url "https://jobs.ashbyhq.com/aiprise/e7890d9f-8e1f-48a0-92be-071a282e7fe8" --company "AiPrise" --title "Software Engineer III (Bangalore, India)"</t>
+          <t>node scripts/tailor.mjs --url "https://jobs.ashbyhq.com/supabase/06752423-eebb-472c-95b5-c7ff2559fd60" --company "Supabase" --title "Software Engineer - Branching"</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr"/>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>On-site or hybrid at a named Indian location.</t>
+          <t>Worldwide or "anywhere" with no country lock stated.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>lever</t>
+          <t>workable</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Agentic Engineer Level II/III</t>
+          <t>4423- Software Development Engineer-II Backend</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Netomi</t>
+          <t>Innovaccer</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr"/>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Remote - India</t>
+          <t>Noida, Uttar Pradesh, India</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1011,14 +1003,18 @@
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr"/>
-      <c r="I8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>5+ yrs</t>
+        </is>
+      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="K8" s="2" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
@@ -1027,18 +1023,18 @@
       </c>
       <c r="M8" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/netomi/0e6b7355-330a-4d10-b8d5-c235bd555622</t>
+          <t>https://apply.workable.com/j/6FB4B40CD6</t>
         </is>
       </c>
       <c r="N8" s="6" t="inlineStr">
         <is>
-          <t>node scripts/tailor.mjs --url "https://jobs.lever.co/netomi/0e6b7355-330a-4d10-b8d5-c235bd555622" --company "Netomi" --title "Agentic Engineer Level II/III"</t>
+          <t>node scripts/tailor.mjs --url "https://apply.workable.com/j/6FB4B40CD6" --company "Innovaccer" --title "4423- Software Development Engineer-II Backend"</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr"/>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>Remote and India is named explicitly.</t>
+          <t>On-site or hybrid at a named Indian location.</t>
         </is>
       </c>
     </row>
@@ -1050,18 +1046,18 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Applied AI Engineer - India</t>
+          <t>Intermediate Backend Engineer - Database Change Management</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Dscout</t>
+          <t>GitLab</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr"/>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Remote - India</t>
+          <t>Bangalore, India</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1071,22 +1067,18 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>india</t>
+          <t>remote-global</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr"/>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>2+ yrs</t>
-        </is>
-      </c>
+      <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="K9" s="2" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
@@ -1095,41 +1087,41 @@
       </c>
       <c r="M9" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/dscout/jobs/4370258009</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8722304002</t>
         </is>
       </c>
       <c r="N9" s="6" t="inlineStr">
         <is>
-          <t>node scripts/tailor.mjs --url "https://job-boards.greenhouse.io/dscout/jobs/4370258009" --company "Dscout" --title "Applied AI Engineer - India"</t>
+          <t>node scripts/tailor.mjs --url "https://job-boards.greenhouse.io/gitlab/jobs/8722304002" --company "GitLab" --title "Intermediate Backend Engineer - Database Change Management"</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr"/>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>Remote and India is named explicitly.</t>
+          <t>On-site or hybrid at a named Indian location.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>ashby</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Software Engineer - India</t>
+          <t>Software Engineer II (Bangalore, India)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Dscout</t>
+          <t>AiPrise</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr"/>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Remote - India</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1150,11 +1142,11 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="K10" s="2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
@@ -1163,18 +1155,18 @@
       </c>
       <c r="M10" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/dscout/jobs/4370266009</t>
+          <t>https://jobs.ashbyhq.com/aiprise/02112df8-70fa-4133-a860-151b5f585ed9</t>
         </is>
       </c>
       <c r="N10" s="6" t="inlineStr">
         <is>
-          <t>node scripts/tailor.mjs --url "https://job-boards.greenhouse.io/dscout/jobs/4370266009" --company "Dscout" --title "Software Engineer - India"</t>
+          <t>node scripts/tailor.mjs --url "https://jobs.ashbyhq.com/aiprise/02112df8-70fa-4133-a860-151b5f585ed9" --company "AiPrise" --title "Software Engineer II (Bangalore, India)"</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr"/>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>Remote and India is named explicitly.</t>
+          <t>On-site or hybrid at a named Indian location.</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1178,12 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Agent Engineer</t>
+          <t>Software Engineer I (Bangalore, India)</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Sarvam AI</t>
+          <t>AiPrise</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr"/>
@@ -1214,11 +1206,11 @@
       <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="K11" s="2" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
@@ -1227,12 +1219,12 @@
       </c>
       <c r="M11" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/sarvam/36f89b00-2010-4d23-aae3-17a2f53d9eaa</t>
+          <t>https://jobs.ashbyhq.com/aiprise/3763c791-a387-4078-9ca4-00cbfbf9b1a6</t>
         </is>
       </c>
       <c r="N11" s="6" t="inlineStr">
         <is>
-          <t>node scripts/tailor.mjs --url "https://jobs.ashbyhq.com/sarvam/36f89b00-2010-4d23-aae3-17a2f53d9eaa" --company "Sarvam AI" --title "Agent Engineer"</t>
+          <t>node scripts/tailor.mjs --url "https://jobs.ashbyhq.com/aiprise/3763c791-a387-4078-9ca4-00cbfbf9b1a6" --company "AiPrise" --title "Software Engineer I (Bangalore, India)"</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr"/>
@@ -1245,23 +1237,23 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>ashby</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Strategic Solutions Engineer, West</t>
+          <t>Software Engineer III (Bangalore, India)</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Glean</t>
+          <t>AiPrise</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr"/>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1271,18 +1263,22 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>remote-global</t>
+          <t>india</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>4+ yrs</t>
+        </is>
+      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="K12" s="2" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
@@ -1291,18 +1287,18 @@
       </c>
       <c r="M12" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gleanwork/jobs/4722386005</t>
+          <t>https://jobs.ashbyhq.com/aiprise/e7890d9f-8e1f-48a0-92be-071a282e7fe8</t>
         </is>
       </c>
       <c r="N12" s="6" t="inlineStr">
         <is>
-          <t>node scripts/tailor.mjs --url "https://job-boards.greenhouse.io/gleanwork/jobs/4722386005" --company "Glean" --title "Strategic Solutions Engineer, West"</t>
+          <t>node scripts/tailor.mjs --url "https://jobs.ashbyhq.com/aiprise/e7890d9f-8e1f-48a0-92be-071a282e7fe8" --company "AiPrise" --title "Software Engineer III (Bangalore, India)"</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr"/>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>Plain "Remote" with no country lock stated. Verify India eligibility on the JD before applying. | Negative keywords: servicenow</t>
+          <t>On-site or hybrid at a named Indian location.</t>
         </is>
       </c>
     </row>
@@ -1314,18 +1310,18 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Software Engineer - India</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Razorpay</t>
+          <t>Dscout</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr"/>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Remote - India</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1339,14 +1335,18 @@
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr"/>
-      <c r="I13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2+ yrs</t>
+        </is>
+      </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="K13" s="2" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
@@ -1355,18 +1355,18 @@
       </c>
       <c r="M13" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4723067005</t>
+          <t>https://job-boards.greenhouse.io/dscout/jobs/4370266009</t>
         </is>
       </c>
       <c r="N13" s="6" t="inlineStr">
         <is>
-          <t>node scripts/tailor.mjs --url "https://job-boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4723067005" --company "Razorpay" --title "Forward Deployed Engineer"</t>
+          <t>node scripts/tailor.mjs --url "https://job-boards.greenhouse.io/dscout/jobs/4370266009" --company "Dscout" --title "Software Engineer - India"</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr"/>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>On-site or hybrid at a named Indian location. | Negative keywords: salesforce</t>
+          <t>Remote and India is named explicitly.</t>
         </is>
       </c>
     </row>
@@ -1378,12 +1378,12 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Experienced Software Engineer</t>
+          <t>Strategic Solutions Engineer, West</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Automattic</t>
+          <t>Glean</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr"/>
@@ -1406,11 +1406,11 @@
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="K14" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
@@ -1419,87 +1419,23 @@
       </c>
       <c r="M14" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/automatticcareers/jobs/5862239</t>
+          <t>https://job-boards.greenhouse.io/gleanwork/jobs/4722386005</t>
         </is>
       </c>
       <c r="N14" s="6" t="inlineStr">
         <is>
-          <t>node scripts/tailor.mjs --url "https://job-boards.greenhouse.io/automatticcareers/jobs/5862239" --company "Automattic" --title "Experienced Software Engineer"</t>
+          <t>node scripts/tailor.mjs --url "https://job-boards.greenhouse.io/gleanwork/jobs/4722386005" --company "Glean" --title "Strategic Solutions Engineer, West"</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr"/>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>Plain "Remote" with no country lock stated. Verify India eligibility on the JD before applying. | Negative keywords: wordpress</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>greenhouse</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Software Engineer, Agents Governance</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Glean</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr"/>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>Bangalore, India</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>india</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr"/>
-      <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="L15" s="4" t="inlineStr">
-        <is>
-          <t>Apply →</t>
-        </is>
-      </c>
-      <c r="M15" s="5" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/gleanwork/jobs/4712434005</t>
-        </is>
-      </c>
-      <c r="N15" s="6" t="inlineStr">
-        <is>
-          <t>node scripts/tailor.mjs --url "https://job-boards.greenhouse.io/gleanwork/jobs/4712434005" --company "Glean" --title "Software Engineer, Agents Governance"</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr"/>
-      <c r="P15" s="3" t="inlineStr">
-        <is>
-          <t>On-site or hybrid at a named Indian location. | Seniority: JD asks for 6+ years vs 2.7 — beyond the stretch band · Negative keywords: servicenow</t>
+          <t>Plain "Remote" with no country lock stated. Verify India eligibility on the JD before applying. | Negative keywords: servicenow</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P15"/>
+  <autoFilter ref="A1:P14"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId2"/>
@@ -1527,8 +1463,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M14" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="rId28"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/tracker.xlsx
+++ b/reports/tracker.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Founder Targets" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Job Listings'!$A$1:$P$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Job Listings'!$A$1:$Q$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,6 +36,12 @@
     </font>
     <font>
       <name val="Arial"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00197A55"/>
       <sz val="10"/>
     </font>
     <font>
@@ -63,7 +69,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -80,6 +86,11 @@
         <fgColor rgb="00E3F1EA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D8EEE2"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -93,7 +104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -104,16 +115,19 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -479,7 +493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P14"/>
+  <dimension ref="A1:Q14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -493,11 +507,12 @@
     <col width="15" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="52" customWidth="1" min="13" max="13"/>
-    <col width="60" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="40" customWidth="1" min="16" max="16"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="50" customWidth="1" min="14" max="14"/>
+    <col width="58" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="38" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -558,25 +573,30 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>Send Resume</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>Apply</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>JD Link</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Tailor Command</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Applied?</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -626,21 +646,26 @@
       </c>
       <c r="L2" s="4" t="inlineStr">
         <is>
+          <t>MERN (check)</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
           <t>Apply →</t>
         </is>
       </c>
-      <c r="M2" s="5" t="inlineStr">
+      <c r="N2" s="6" t="inlineStr">
         <is>
           <t>https://jobs.lever.co/gohighlevel/13c8402f-8cf0-4b09-b666-43e71b8b525e</t>
         </is>
       </c>
-      <c r="N2" s="6" t="inlineStr">
+      <c r="O2" s="7" t="inlineStr">
         <is>
           <t>node scripts/tailor.mjs --url "https://jobs.lever.co/gohighlevel/13c8402f-8cf0-4b09-b666-43e71b8b525e" --company "HighLevel (GoHighLevel)" --title "Software Development Engineer II - Backend"</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr"/>
-      <c r="P2" s="3" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr"/>
+      <c r="Q2" s="3" t="inlineStr">
         <is>
           <t>On-site or hybrid at a named Indian location.</t>
         </is>
@@ -690,21 +715,26 @@
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
+          <t>MERN (check)</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
           <t>Apply →</t>
         </is>
       </c>
-      <c r="M3" s="5" t="inlineStr">
+      <c r="N3" s="6" t="inlineStr">
         <is>
           <t>https://jobs.lever.co/gohighlevel/b8dc97ec-a0b7-4195-9f3b-86440ff18f82</t>
         </is>
       </c>
-      <c r="N3" s="6" t="inlineStr">
+      <c r="O3" s="7" t="inlineStr">
         <is>
           <t>node scripts/tailor.mjs --url "https://jobs.lever.co/gohighlevel/b8dc97ec-a0b7-4195-9f3b-86440ff18f82" --company "HighLevel (GoHighLevel)" --title "Software Development Engineer II - Frontend"</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr"/>
-      <c r="P3" s="3" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr"/>
+      <c r="Q3" s="3" t="inlineStr">
         <is>
           <t>On-site or hybrid at a named Indian location.</t>
         </is>
@@ -754,21 +784,26 @@
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
+          <t>MERN (check)</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
           <t>Apply →</t>
         </is>
       </c>
-      <c r="M4" s="5" t="inlineStr">
+      <c r="N4" s="6" t="inlineStr">
         <is>
           <t>https://apply.workable.com/j/E7CD7FB957</t>
         </is>
       </c>
-      <c r="N4" s="6" t="inlineStr">
+      <c r="O4" s="7" t="inlineStr">
         <is>
           <t>node scripts/tailor.mjs --url "https://apply.workable.com/j/E7CD7FB957" --company "Innovaccer" --title "4403 - Software Development Engineer-II (Finance - AI Engineering)"</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr"/>
-      <c r="P4" s="3" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr"/>
+      <c r="Q4" s="3" t="inlineStr">
         <is>
           <t>On-site or hybrid at a named Indian location. | Weak archetype match (best: sde-generalist @ 16)</t>
         </is>
@@ -818,21 +853,26 @@
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
+          <t>MERN</t>
+        </is>
+      </c>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
           <t>Apply →</t>
         </is>
       </c>
-      <c r="M5" s="5" t="inlineStr">
+      <c r="N5" s="6" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/gitlab/jobs/8775507002</t>
         </is>
       </c>
-      <c r="N5" s="6" t="inlineStr">
+      <c r="O5" s="7" t="inlineStr">
         <is>
           <t>node scripts/tailor.mjs --url "https://job-boards.greenhouse.io/gitlab/jobs/8775507002" --company "GitLab" --title "Intermediate Backend Engineer, India"</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr"/>
-      <c r="P5" s="3" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="3" t="inlineStr">
         <is>
           <t>On-site or hybrid at a named Indian location.</t>
         </is>
@@ -882,21 +922,26 @@
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
+          <t>MERN</t>
+        </is>
+      </c>
+      <c r="M6" s="5" t="inlineStr">
+        <is>
           <t>Apply →</t>
         </is>
       </c>
-      <c r="M6" s="5" t="inlineStr">
+      <c r="N6" s="6" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/gitlab/jobs/8736877002</t>
         </is>
       </c>
-      <c r="N6" s="6" t="inlineStr">
+      <c r="O6" s="7" t="inlineStr">
         <is>
           <t>node scripts/tailor.mjs --url "https://job-boards.greenhouse.io/gitlab/jobs/8736877002" --company "GitLab" --title "Intermediate Backend Engineer"</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr"/>
-      <c r="P6" s="3" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="3" t="inlineStr">
         <is>
           <t>On-site or hybrid at a named Indian location.</t>
         </is>
@@ -950,21 +995,26 @@
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
+          <t>MERN</t>
+        </is>
+      </c>
+      <c r="M7" s="5" t="inlineStr">
+        <is>
           <t>Apply →</t>
         </is>
       </c>
-      <c r="M7" s="5" t="inlineStr">
+      <c r="N7" s="6" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/supabase/06752423-eebb-472c-95b5-c7ff2559fd60</t>
         </is>
       </c>
-      <c r="N7" s="6" t="inlineStr">
+      <c r="O7" s="7" t="inlineStr">
         <is>
           <t>node scripts/tailor.mjs --url "https://jobs.ashbyhq.com/supabase/06752423-eebb-472c-95b5-c7ff2559fd60" --company "Supabase" --title "Software Engineer - Branching"</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr"/>
-      <c r="P7" s="3" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr"/>
+      <c r="Q7" s="3" t="inlineStr">
         <is>
           <t>Worldwide or "anywhere" with no country lock stated.</t>
         </is>
@@ -1018,21 +1068,26 @@
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
+          <t>MERN</t>
+        </is>
+      </c>
+      <c r="M8" s="5" t="inlineStr">
+        <is>
           <t>Apply →</t>
         </is>
       </c>
-      <c r="M8" s="5" t="inlineStr">
+      <c r="N8" s="6" t="inlineStr">
         <is>
           <t>https://apply.workable.com/j/6FB4B40CD6</t>
         </is>
       </c>
-      <c r="N8" s="6" t="inlineStr">
+      <c r="O8" s="7" t="inlineStr">
         <is>
           <t>node scripts/tailor.mjs --url "https://apply.workable.com/j/6FB4B40CD6" --company "Innovaccer" --title "4423- Software Development Engineer-II Backend"</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr"/>
-      <c r="P8" s="3" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="3" t="inlineStr">
         <is>
           <t>On-site or hybrid at a named Indian location.</t>
         </is>
@@ -1082,21 +1137,26 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
+          <t>MERN</t>
+        </is>
+      </c>
+      <c r="M9" s="5" t="inlineStr">
+        <is>
           <t>Apply →</t>
         </is>
       </c>
-      <c r="M9" s="5" t="inlineStr">
+      <c r="N9" s="6" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/gitlab/jobs/8722304002</t>
         </is>
       </c>
-      <c r="N9" s="6" t="inlineStr">
+      <c r="O9" s="7" t="inlineStr">
         <is>
           <t>node scripts/tailor.mjs --url "https://job-boards.greenhouse.io/gitlab/jobs/8722304002" --company "GitLab" --title "Intermediate Backend Engineer - Database Change Management"</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr"/>
-      <c r="P9" s="3" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="3" t="inlineStr">
         <is>
           <t>On-site or hybrid at a named Indian location.</t>
         </is>
@@ -1150,21 +1210,26 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
+          <t>MERN</t>
+        </is>
+      </c>
+      <c r="M10" s="5" t="inlineStr">
+        <is>
           <t>Apply →</t>
         </is>
       </c>
-      <c r="M10" s="5" t="inlineStr">
+      <c r="N10" s="6" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/aiprise/02112df8-70fa-4133-a860-151b5f585ed9</t>
         </is>
       </c>
-      <c r="N10" s="6" t="inlineStr">
+      <c r="O10" s="7" t="inlineStr">
         <is>
           <t>node scripts/tailor.mjs --url "https://jobs.ashbyhq.com/aiprise/02112df8-70fa-4133-a860-151b5f585ed9" --company "AiPrise" --title "Software Engineer II (Bangalore, India)"</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr"/>
-      <c r="P10" s="3" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="3" t="inlineStr">
         <is>
           <t>On-site or hybrid at a named Indian location.</t>
         </is>
@@ -1214,21 +1279,26 @@
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
+          <t>MERN</t>
+        </is>
+      </c>
+      <c r="M11" s="5" t="inlineStr">
+        <is>
           <t>Apply →</t>
         </is>
       </c>
-      <c r="M11" s="5" t="inlineStr">
+      <c r="N11" s="6" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/aiprise/3763c791-a387-4078-9ca4-00cbfbf9b1a6</t>
         </is>
       </c>
-      <c r="N11" s="6" t="inlineStr">
+      <c r="O11" s="7" t="inlineStr">
         <is>
           <t>node scripts/tailor.mjs --url "https://jobs.ashbyhq.com/aiprise/3763c791-a387-4078-9ca4-00cbfbf9b1a6" --company "AiPrise" --title "Software Engineer I (Bangalore, India)"</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr"/>
-      <c r="P11" s="3" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="3" t="inlineStr">
         <is>
           <t>On-site or hybrid at a named Indian location.</t>
         </is>
@@ -1282,21 +1352,26 @@
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
+          <t>MERN</t>
+        </is>
+      </c>
+      <c r="M12" s="5" t="inlineStr">
+        <is>
           <t>Apply →</t>
         </is>
       </c>
-      <c r="M12" s="5" t="inlineStr">
+      <c r="N12" s="6" t="inlineStr">
         <is>
           <t>https://jobs.ashbyhq.com/aiprise/e7890d9f-8e1f-48a0-92be-071a282e7fe8</t>
         </is>
       </c>
-      <c r="N12" s="6" t="inlineStr">
+      <c r="O12" s="7" t="inlineStr">
         <is>
           <t>node scripts/tailor.mjs --url "https://jobs.ashbyhq.com/aiprise/e7890d9f-8e1f-48a0-92be-071a282e7fe8" --company "AiPrise" --title "Software Engineer III (Bangalore, India)"</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr"/>
-      <c r="P12" s="3" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="3" t="inlineStr">
         <is>
           <t>On-site or hybrid at a named Indian location.</t>
         </is>
@@ -1350,21 +1425,26 @@
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
+          <t>MERN</t>
+        </is>
+      </c>
+      <c r="M13" s="5" t="inlineStr">
+        <is>
           <t>Apply →</t>
         </is>
       </c>
-      <c r="M13" s="5" t="inlineStr">
+      <c r="N13" s="6" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/dscout/jobs/4370266009</t>
         </is>
       </c>
-      <c r="N13" s="6" t="inlineStr">
+      <c r="O13" s="7" t="inlineStr">
         <is>
           <t>node scripts/tailor.mjs --url "https://job-boards.greenhouse.io/dscout/jobs/4370266009" --company "Dscout" --title "Software Engineer - India"</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr"/>
-      <c r="P13" s="3" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="3" t="inlineStr">
         <is>
           <t>Remote and India is named explicitly.</t>
         </is>
@@ -1414,55 +1494,60 @@
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
+          <t>MERN (check)</t>
+        </is>
+      </c>
+      <c r="M14" s="5" t="inlineStr">
+        <is>
           <t>Apply →</t>
         </is>
       </c>
-      <c r="M14" s="5" t="inlineStr">
+      <c r="N14" s="6" t="inlineStr">
         <is>
           <t>https://job-boards.greenhouse.io/gleanwork/jobs/4722386005</t>
         </is>
       </c>
-      <c r="N14" s="6" t="inlineStr">
+      <c r="O14" s="7" t="inlineStr">
         <is>
           <t>node scripts/tailor.mjs --url "https://job-boards.greenhouse.io/gleanwork/jobs/4722386005" --company "Glean" --title "Strategic Solutions Engineer, West"</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr"/>
-      <c r="P14" s="3" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="3" t="inlineStr">
         <is>
           <t>Plain "Remote" with no country lock stated. Verify India eligibility on the JD before applying. | Negative keywords: servicenow</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P14"/>
+  <autoFilter ref="A1:Q14"/>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L4" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M4" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M3" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M4" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M5" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M14" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N14" r:id="rId26"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1578,7 +1663,7 @@
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>VERIFY BEFORE SENDING — every Guessed Email is a first@domain guess, never a verified address; check it yourself (Hunter.io) first. Personalise every draft with one genuine observation about what they build. Nothing in this tab is ever sent automatically.</t>
         </is>

--- a/reports/tracker.xlsx
+++ b/reports/tracker.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Founder Targets" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Job Listings'!$A$1:$Q$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Job Listings'!$A$1:$Q$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -64,12 +64,18 @@
     </font>
     <font>
       <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001D4ED8"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <i val="1"/>
       <color rgb="009A6206"/>
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -91,6 +97,11 @@
         <fgColor rgb="00D8EEE2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCE9F7"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -104,7 +115,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -127,7 +138,10 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -493,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q14"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -743,23 +757,23 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>workable</t>
+          <t>himalayas</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>4403 - Software Development Engineer-II (Finance - AI Engineering)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Innovaccer</t>
+          <t>Infios</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Noida, Uttar Pradesh, India</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -776,15 +790,15 @@
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="K4" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>MERN (check)</t>
+        <v>0</v>
+      </c>
+      <c r="L4" s="8" t="inlineStr">
+        <is>
+          <t>Mobile (check)</t>
         </is>
       </c>
       <c r="M4" s="5" t="inlineStr">
@@ -794,41 +808,41 @@
       </c>
       <c r="N4" s="6" t="inlineStr">
         <is>
-          <t>https://apply.workable.com/j/E7CD7FB957</t>
+          <t>https://himalayas.app/companies/infios/jobs/software-engineer</t>
         </is>
       </c>
       <c r="O4" s="7" t="inlineStr">
         <is>
-          <t>node scripts/tailor.mjs --url "https://apply.workable.com/j/E7CD7FB957" --company "Innovaccer" --title "4403 - Software Development Engineer-II (Finance - AI Engineering)"</t>
+          <t>node scripts/tailor.mjs --url "https://himalayas.app/companies/infios/jobs/software-engineer" --company "Infios" --title "Software Engineer"</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr"/>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>On-site or hybrid at a named Indian location. | Weak archetype match (best: sde-generalist @ 16)</t>
+          <t>On-site or hybrid at a named Indian location.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>workable</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Intermediate Backend Engineer, India</t>
+          <t>4403 - Software Development Engineer-II (Finance - AI Engineering)</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>GitLab</t>
+          <t>Innovaccer</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr"/>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Bangalore, India</t>
+          <t>Noida, Uttar Pradesh, India</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -838,22 +852,22 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>remote-global</t>
+          <t>india</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
       <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="K5" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>MERN</t>
+          <t>MERN (check)</t>
         </is>
       </c>
       <c r="M5" s="5" t="inlineStr">
@@ -863,18 +877,18 @@
       </c>
       <c r="N5" s="6" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8775507002</t>
+          <t>https://apply.workable.com/j/E7CD7FB957</t>
         </is>
       </c>
       <c r="O5" s="7" t="inlineStr">
         <is>
-          <t>node scripts/tailor.mjs --url "https://job-boards.greenhouse.io/gitlab/jobs/8775507002" --company "GitLab" --title "Intermediate Backend Engineer, India"</t>
+          <t>node scripts/tailor.mjs --url "https://apply.workable.com/j/E7CD7FB957" --company "Innovaccer" --title "4403 - Software Development Engineer-II (Finance - AI Engineering)"</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr"/>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>On-site or hybrid at a named Indian location.</t>
+          <t>On-site or hybrid at a named Indian location. | Weak archetype match (best: sde-generalist @ 16)</t>
         </is>
       </c>
     </row>
@@ -886,7 +900,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Intermediate Backend Engineer</t>
+          <t>Intermediate Backend Engineer, India</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -914,11 +928,11 @@
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="K6" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
@@ -932,12 +946,12 @@
       </c>
       <c r="N6" s="6" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8736877002</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8775507002</t>
         </is>
       </c>
       <c r="O6" s="7" t="inlineStr">
         <is>
-          <t>node scripts/tailor.mjs --url "https://job-boards.greenhouse.io/gitlab/jobs/8736877002" --company "GitLab" --title "Intermediate Backend Engineer"</t>
+          <t>node scripts/tailor.mjs --url "https://job-boards.greenhouse.io/gitlab/jobs/8775507002" --company "GitLab" --title "Intermediate Backend Engineer, India"</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr"/>
@@ -950,23 +964,23 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>ashby</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Software Engineer - Branching</t>
+          <t>Intermediate Backend Engineer</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Supabase</t>
+          <t>GitLab</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr"/>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Remote, Global</t>
+          <t>Bangalore, India</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -980,18 +994,14 @@
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr"/>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3+ yrs</t>
-        </is>
-      </c>
+      <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="K7" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
@@ -1005,41 +1015,41 @@
       </c>
       <c r="N7" s="6" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/supabase/06752423-eebb-472c-95b5-c7ff2559fd60</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8736877002</t>
         </is>
       </c>
       <c r="O7" s="7" t="inlineStr">
         <is>
-          <t>node scripts/tailor.mjs --url "https://jobs.ashbyhq.com/supabase/06752423-eebb-472c-95b5-c7ff2559fd60" --company "Supabase" --title "Software Engineer - Branching"</t>
+          <t>node scripts/tailor.mjs --url "https://job-boards.greenhouse.io/gitlab/jobs/8736877002" --company "GitLab" --title "Intermediate Backend Engineer"</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr"/>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>Worldwide or "anywhere" with no country lock stated.</t>
+          <t>On-site or hybrid at a named Indian location.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>workable</t>
+          <t>hn-whoishiring</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>4423- Software Development Engineer-II Backend</t>
+          <t>Backend Software Engineer</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Innovaccer</t>
+          <t>Enveritas (YC S18, non-profit)</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr"/>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Noida, Uttar Pradesh, India</t>
+          <t>Remote (Global), https://enveritas, Global</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1049,26 +1059,22 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>india</t>
+          <t>remote-global</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr"/>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>5+ yrs</t>
-        </is>
-      </c>
+      <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
         <is>
           <t>2026-09-02</t>
         </is>
       </c>
       <c r="K8" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>MERN</t>
+          <t>MERN (check)</t>
         </is>
       </c>
       <c r="M8" s="5" t="inlineStr">
@@ -1078,41 +1084,41 @@
       </c>
       <c r="N8" s="6" t="inlineStr">
         <is>
-          <t>https://apply.workable.com/j/6FB4B40CD6</t>
+          <t>https://news.ycombinator.com/item?id=49541107</t>
         </is>
       </c>
       <c r="O8" s="7" t="inlineStr">
         <is>
-          <t>node scripts/tailor.mjs --url "https://apply.workable.com/j/6FB4B40CD6" --company "Innovaccer" --title "4423- Software Development Engineer-II Backend"</t>
+          <t>node scripts/tailor.mjs --url "https://news.ycombinator.com/item?id=49541107" --company "Enveritas (YC S18, non-profit)" --title "Backend Software Engineer"</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr"/>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>On-site or hybrid at a named Indian location.</t>
+          <t>Plain "Remote" with no country lock stated. Verify India eligibility on the JD before applying.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>hn-whoishiring</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Intermediate Backend Engineer - Database Change Management</t>
+          <t>Product Engineer</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>GitLab</t>
+          <t>Colonist</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr"/>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Bangalore, India</t>
+          <t>Full-time, Remote &amp; async Colonist</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1129,15 +1135,15 @@
       <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="K9" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="L9" s="4" t="inlineStr">
-        <is>
-          <t>MERN</t>
+        <v>6</v>
+      </c>
+      <c r="L9" s="8" t="inlineStr">
+        <is>
+          <t>Mobile (check)</t>
         </is>
       </c>
       <c r="M9" s="5" t="inlineStr">
@@ -1147,18 +1153,18 @@
       </c>
       <c r="N9" s="6" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gitlab/jobs/8722304002</t>
+          <t>https://news.ycombinator.com/item?id=49550510</t>
         </is>
       </c>
       <c r="O9" s="7" t="inlineStr">
         <is>
-          <t>node scripts/tailor.mjs --url "https://job-boards.greenhouse.io/gitlab/jobs/8722304002" --company "GitLab" --title "Intermediate Backend Engineer - Database Change Management"</t>
+          <t>node scripts/tailor.mjs --url "https://news.ycombinator.com/item?id=49550510" --company "Colonist" --title "Product Engineer"</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr"/>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>On-site or hybrid at a named Indian location.</t>
+          <t>Plain "Remote" with no country lock stated. Verify India eligibility on the JD before applying. | Weak archetype match (best: sde-generalist @ 6)</t>
         </is>
       </c>
     </row>
@@ -1170,18 +1176,18 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Software Engineer II (Bangalore, India)</t>
+          <t>Software Engineer - Branching</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>AiPrise</t>
+          <t>Supabase</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr"/>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Remote, Global</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1191,22 +1197,22 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>india</t>
+          <t>remote-global</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2+ yrs</t>
+          <t>3+ yrs</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="K10" s="2" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
@@ -1220,41 +1226,41 @@
       </c>
       <c r="N10" s="6" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/aiprise/02112df8-70fa-4133-a860-151b5f585ed9</t>
+          <t>https://jobs.ashbyhq.com/supabase/06752423-eebb-472c-95b5-c7ff2559fd60</t>
         </is>
       </c>
       <c r="O10" s="7" t="inlineStr">
         <is>
-          <t>node scripts/tailor.mjs --url "https://jobs.ashbyhq.com/aiprise/02112df8-70fa-4133-a860-151b5f585ed9" --company "AiPrise" --title "Software Engineer II (Bangalore, India)"</t>
+          <t>node scripts/tailor.mjs --url "https://jobs.ashbyhq.com/supabase/06752423-eebb-472c-95b5-c7ff2559fd60" --company "Supabase" --title "Software Engineer - Branching"</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr"/>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>On-site or hybrid at a named Indian location.</t>
+          <t>Worldwide or "anywhere" with no country lock stated.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>ashby</t>
+          <t>workable</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Software Engineer I (Bangalore, India)</t>
+          <t>4423- Software Development Engineer-II Backend</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>AiPrise</t>
+          <t>Innovaccer</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr"/>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Noida, Uttar Pradesh, India</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1268,14 +1274,18 @@
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr"/>
-      <c r="I11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>5+ yrs</t>
+        </is>
+      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="K11" s="2" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
@@ -1289,12 +1299,12 @@
       </c>
       <c r="N11" s="6" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/aiprise/3763c791-a387-4078-9ca4-00cbfbf9b1a6</t>
+          <t>https://apply.workable.com/j/6FB4B40CD6</t>
         </is>
       </c>
       <c r="O11" s="7" t="inlineStr">
         <is>
-          <t>node scripts/tailor.mjs --url "https://jobs.ashbyhq.com/aiprise/3763c791-a387-4078-9ca4-00cbfbf9b1a6" --company "AiPrise" --title "Software Engineer I (Bangalore, India)"</t>
+          <t>node scripts/tailor.mjs --url "https://apply.workable.com/j/6FB4B40CD6" --company "Innovaccer" --title "4423- Software Development Engineer-II Backend"</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr"/>
@@ -1307,23 +1317,23 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ashby</t>
+          <t>hn-whoishiring</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Software Engineer III (Bangalore, India)</t>
+          <t>Forward-Deployed Engineer (FDE)</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>AiPrise</t>
+          <t>Shovels</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr"/>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1333,26 +1343,22 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>india</t>
+          <t>remote-global</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>4+ yrs</t>
-        </is>
-      </c>
+      <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="K12" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>MERN</t>
+          <t>MERN (check)</t>
         </is>
       </c>
       <c r="M12" s="5" t="inlineStr">
@@ -1362,18 +1368,18 @@
       </c>
       <c r="N12" s="6" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/aiprise/e7890d9f-8e1f-48a0-92be-071a282e7fe8</t>
+          <t>https://news.ycombinator.com/item?id=49530020</t>
         </is>
       </c>
       <c r="O12" s="7" t="inlineStr">
         <is>
-          <t>node scripts/tailor.mjs --url "https://jobs.ashbyhq.com/aiprise/e7890d9f-8e1f-48a0-92be-071a282e7fe8" --company "AiPrise" --title "Software Engineer III (Bangalore, India)"</t>
+          <t>node scripts/tailor.mjs --url "https://news.ycombinator.com/item?id=49530020" --company "Shovels" --title "Forward-Deployed Engineer (FDE)"</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr"/>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t>On-site or hybrid at a named Indian location.</t>
+          <t>Plain "Remote" with no country lock stated. Verify India eligibility on the JD before applying. | Weak archetype match (best: forward-deployed-engineer @ 13)</t>
         </is>
       </c>
     </row>
@@ -1385,18 +1391,18 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Software Engineer - India</t>
+          <t>Intermediate Backend Engineer - Database Change Management</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Dscout</t>
+          <t>GitLab</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr"/>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Remote - India</t>
+          <t>Bangalore, India</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1406,22 +1412,18 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>india</t>
+          <t>remote-global</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr"/>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2+ yrs</t>
-        </is>
-      </c>
+      <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="K13" s="2" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
@@ -1435,41 +1437,41 @@
       </c>
       <c r="N13" s="6" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/dscout/jobs/4370266009</t>
+          <t>https://job-boards.greenhouse.io/gitlab/jobs/8722304002</t>
         </is>
       </c>
       <c r="O13" s="7" t="inlineStr">
         <is>
-          <t>node scripts/tailor.mjs --url "https://job-boards.greenhouse.io/dscout/jobs/4370266009" --company "Dscout" --title "Software Engineer - India"</t>
+          <t>node scripts/tailor.mjs --url "https://job-boards.greenhouse.io/gitlab/jobs/8722304002" --company "GitLab" --title "Intermediate Backend Engineer - Database Change Management"</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr"/>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t>Remote and India is named explicitly.</t>
+          <t>On-site or hybrid at a named Indian location.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>hn-whoishiring</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Strategic Solutions Engineer, West</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Glean</t>
+          <t>OpenAlex</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr"/>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Remote, Full-time</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1486,11 +1488,11 @@
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="K14" s="2" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
@@ -1504,23 +1506,518 @@
       </c>
       <c r="N14" s="6" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/gleanwork/jobs/4722386005</t>
+          <t>https://news.ycombinator.com/item?id=49524920</t>
         </is>
       </c>
       <c r="O14" s="7" t="inlineStr">
         <is>
-          <t>node scripts/tailor.mjs --url "https://job-boards.greenhouse.io/gleanwork/jobs/4722386005" --company "Glean" --title "Strategic Solutions Engineer, West"</t>
+          <t>node scripts/tailor.mjs --url "https://news.ycombinator.com/item?id=49524920" --company "OpenAlex" --title "Software Engineer"</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr"/>
       <c r="Q14" s="3" t="inlineStr">
         <is>
+          <t>Plain "Remote" with no country lock stated. Verify India eligibility on the JD before applying.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>hn-whoishiring</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Backend Systems Engineer (Rust)</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Proxybase</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr"/>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Remote, Global, Full-Time Hi HN, I’m the founder of Proxybase [0]</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>remote-global</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>MERN</t>
+        </is>
+      </c>
+      <c r="M15" s="5" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="N15" s="6" t="inlineStr">
+        <is>
+          <t>https://news.ycombinator.com/item?id=49523422</t>
+        </is>
+      </c>
+      <c r="O15" s="7" t="inlineStr">
+        <is>
+          <t>node scripts/tailor.mjs --url "https://news.ycombinator.com/item?id=49523422" --company "Proxybase" --title "Backend Systems Engineer (Rust)"</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="3" t="inlineStr">
+        <is>
+          <t>Worldwide or "anywhere" with no country lock stated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>hn-whoishiring</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Fullstack SWE</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Quill</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr"/>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Full-time, Remote, PT/ET hours preferred, $150 - 210K USD + equity, https://quill</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>remote-global</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="L16" s="4" t="inlineStr">
+        <is>
+          <t>MERN</t>
+        </is>
+      </c>
+      <c r="M16" s="5" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="N16" s="6" t="inlineStr">
+        <is>
+          <t>https://news.ycombinator.com/item?id=49522912</t>
+        </is>
+      </c>
+      <c r="O16" s="7" t="inlineStr">
+        <is>
+          <t>node scripts/tailor.mjs --url "https://news.ycombinator.com/item?id=49522912" --company "Quill" --title "Fullstack SWE"</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr"/>
+      <c r="Q16" s="3" t="inlineStr">
+        <is>
+          <t>Plain "Remote" with no country lock stated. Verify India eligibility on the JD before applying.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>ashby</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer II (Bangalore, India)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>AiPrise</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr"/>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>india</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>2+ yrs</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>MERN</t>
+        </is>
+      </c>
+      <c r="M17" s="5" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="N17" s="6" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/aiprise/02112df8-70fa-4133-a860-151b5f585ed9</t>
+        </is>
+      </c>
+      <c r="O17" s="7" t="inlineStr">
+        <is>
+          <t>node scripts/tailor.mjs --url "https://jobs.ashbyhq.com/aiprise/02112df8-70fa-4133-a860-151b5f585ed9" --company "AiPrise" --title "Software Engineer II (Bangalore, India)"</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr"/>
+      <c r="Q17" s="3" t="inlineStr">
+        <is>
+          <t>On-site or hybrid at a named Indian location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>ashby</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer I (Bangalore, India)</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>AiPrise</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr"/>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>india</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t>MERN</t>
+        </is>
+      </c>
+      <c r="M18" s="5" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="N18" s="6" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/aiprise/3763c791-a387-4078-9ca4-00cbfbf9b1a6</t>
+        </is>
+      </c>
+      <c r="O18" s="7" t="inlineStr">
+        <is>
+          <t>node scripts/tailor.mjs --url "https://jobs.ashbyhq.com/aiprise/3763c791-a387-4078-9ca4-00cbfbf9b1a6" --company "AiPrise" --title "Software Engineer I (Bangalore, India)"</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="3" t="inlineStr">
+        <is>
+          <t>On-site or hybrid at a named Indian location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>ashby</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer III (Bangalore, India)</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>AiPrise</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr"/>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>india</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>4+ yrs</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>MERN</t>
+        </is>
+      </c>
+      <c r="M19" s="5" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="N19" s="6" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/aiprise/e7890d9f-8e1f-48a0-92be-071a282e7fe8</t>
+        </is>
+      </c>
+      <c r="O19" s="7" t="inlineStr">
+        <is>
+          <t>node scripts/tailor.mjs --url "https://jobs.ashbyhq.com/aiprise/e7890d9f-8e1f-48a0-92be-071a282e7fe8" --company "AiPrise" --title "Software Engineer III (Bangalore, India)"</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr"/>
+      <c r="Q19" s="3" t="inlineStr">
+        <is>
+          <t>On-site or hybrid at a named Indian location.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Software Engineer - India</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Dscout</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr"/>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Remote - India</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>india</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>2+ yrs</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>MERN</t>
+        </is>
+      </c>
+      <c r="M20" s="5" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="N20" s="6" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/dscout/jobs/4370266009</t>
+        </is>
+      </c>
+      <c r="O20" s="7" t="inlineStr">
+        <is>
+          <t>node scripts/tailor.mjs --url "https://job-boards.greenhouse.io/dscout/jobs/4370266009" --company "Dscout" --title "Software Engineer - India"</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr"/>
+      <c r="Q20" s="3" t="inlineStr">
+        <is>
+          <t>Remote and India is named explicitly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>greenhouse</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Strategic Solutions Engineer, West</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Glean</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr"/>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>remote-global</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>MERN (check)</t>
+        </is>
+      </c>
+      <c r="M21" s="5" t="inlineStr">
+        <is>
+          <t>Apply →</t>
+        </is>
+      </c>
+      <c r="N21" s="6" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/gleanwork/jobs/4722386005</t>
+        </is>
+      </c>
+      <c r="O21" s="7" t="inlineStr">
+        <is>
+          <t>node scripts/tailor.mjs --url "https://job-boards.greenhouse.io/gleanwork/jobs/4722386005" --company "Glean" --title "Strategic Solutions Engineer, West"</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr"/>
+      <c r="Q21" s="3" t="inlineStr">
+        <is>
           <t>Plain "Remote" with no country lock stated. Verify India eligibility on the JD before applying. | Negative keywords: servicenow</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q14"/>
+  <autoFilter ref="A1:Q21"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId2"/>
@@ -1548,6 +2045,20 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N13" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M14" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M16" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M17" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N17" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N18" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M19" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N19" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M20" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N20" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M21" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N21" r:id="rId40"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1663,7 +2174,7 @@
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>VERIFY BEFORE SENDING — every Guessed Email is a first@domain guess, never a verified address; check it yourself (Hunter.io) first. Personalise every draft with one genuine observation about what they build. Nothing in this tab is ever sent automatically.</t>
         </is>
